--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169959억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169925억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 178831억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 178760억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 165091억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164983억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164564억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164420억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 163090억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162942억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169959억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169925억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 178831억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 178760억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 165091억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164983억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164564억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164420억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 163090억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162942억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2052,13 +2052,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22053억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22052억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22346억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22345억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2112,13 +2112,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22053억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22052억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22346억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22345억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4174,7 +4174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5045,35 +5045,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5164,35 +5164,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5283,35 +5283,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5402,35 +5402,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5521,35 +5521,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5640,35 +5640,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5759,35 +5759,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5878,35 +5878,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6104,7 +6104,7 @@
         <v>87900</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>83000</v>
+        <v>89600</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6286,7 +6286,7 @@
         <v>70688.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>80350</v>
+        <v>80900</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6454,20 +6454,20 @@
         <v>0.26688849</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.32951657</v>
+        <v>0.329252956</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.391639157</v>
+        <v>0.391086336</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.100651074</v>
+        <v>0.099932458</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.021701944</v>
+        <v>0.020803194</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.040417313</v>
+        <v>-0.041095712</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6768,23 +6768,23 @@
         <v>0.044952253</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.044952243</v>
+        <v>0.044952166</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.044952374</v>
+        <v>0.044951897</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.044952021</v>
+        <v>0.044951933</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.044952287</v>
+        <v>0.044952329</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.044952119</v>
+        <v>0.044952208</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7944,36 +7944,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.009521796000000001</v>
+        <v>0.010074078</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.001767136</v>
+        <v>0.00088837</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.006666156</v>
+        <v>0.005243993</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>934.962741254</v>
+        <v>934.960322591</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.003395051</v>
+        <v>0.003672331</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.0018489</v>
+        <v>-0.000856926</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.01158005</v>
+        <v>-0.00366001</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>934.959049005</v>
+        <v>934.964663045</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.008346219</v>
+        <v>-0.001171286</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.00020001</v>
+        <v>0.004067527</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.009621796</v>
+        <v>0.010174078</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.001767136</v>
+        <v>0.00088837</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.006666156</v>
+        <v>0.005243993</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>934.962741254</v>
+        <v>934.960322591</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.003395051</v>
+        <v>0.003672331</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.0018489</v>
+        <v>-0.000856926</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.01158005</v>
+        <v>-0.00366001</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>934.959049005</v>
+        <v>934.964663045</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.008346219</v>
+        <v>-0.001171286</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.00020001</v>
+        <v>0.004067527</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8344,20 +8344,20 @@
         <v>-0.016820258</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.033142947</v>
+        <v>-0.03313443</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.01463287</v>
+        <v>-0.014622045</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.040569309</v>
+        <v>0.040588938</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.01801066</v>
+        <v>-0.017983579</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.032315917</v>
+        <v>-0.032273162</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8472,20 +8472,20 @@
         <v>0.013002672</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.024865545</v>
+        <v>0.024859155</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.010356947</v>
+        <v>0.010349441</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.028004194</v>
+        <v>-0.028018681</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.013309499</v>
+        <v>0.01329038</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.023142658</v>
+        <v>0.023114667</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1826167986110005</v>
+        <v>0.1826198982641148</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07578078765413036</v>
+        <v>0.07578076200067632</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02312830803283635</v>
+        <v>0.02310819356317076</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.04269861740915402</v>
+        <v>0.04268507342716227</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33839,7 +33839,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169925억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169896억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 178760억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 178685억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164983억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164865억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164420억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164256억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162942억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 162764억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169925억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169896억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 178760억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 178685억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164983억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164865억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164420억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164256억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162942억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 162764억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2046,19 +2046,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22688억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22687억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22052억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22051억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22345억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22344억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2106,19 +2106,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22688억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22687억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22052억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22051억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22345억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22344억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4174,7 +4174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5045,35 +5045,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5164,35 +5164,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5283,35 +5283,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5402,35 +5402,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5521,35 +5521,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5640,35 +5640,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5759,35 +5759,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5878,35 +5878,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6013,7 +6013,7 @@
         <v>75200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>82000</v>
+        <v>78100</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6286,7 +6286,7 @@
         <v>70688.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>80900</v>
+        <v>80150</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6454,20 +6454,20 @@
         <v>0.26688849</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.329252956</v>
+        <v>0.329026526</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.391086336</v>
+        <v>0.390508</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.099932458</v>
+        <v>0.099141566</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.020803194</v>
+        <v>0.019789578</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.041095712</v>
+        <v>-0.041983055</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6768,23 +6768,23 @@
         <v>0.044952253</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.044952166</v>
+        <v>0.044952331</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.044951897</v>
+        <v>0.044952244</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.044951933</v>
+        <v>0.044952534</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.044952329</v>
+        <v>0.044952106</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.044952208</v>
+        <v>0.044952487</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7944,36 +7944,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.010074078</v>
+        <v>0.01110209</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.00088837</v>
+        <v>0.003120246</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.005243993</v>
+        <v>0.007004925</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>934.960322591</v>
+        <v>934.962964736</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.003672331</v>
+        <v>0.005121293</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>-0.000856926</v>
+        <v>0.009785245999999999</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.00366001</v>
+        <v>-0.003100619</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>934.964663045</v>
+        <v>934.973496008</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>-0.001171286</v>
+        <v>0.005821684</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.004067527</v>
+        <v>0.004293154</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.010174078</v>
+        <v>0.01120209</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.00088837</v>
+        <v>0.003120246</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.005243993</v>
+        <v>0.007004925</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>934.960322591</v>
+        <v>934.962964736</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.003672331</v>
+        <v>0.005121293</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>-0.000856926</v>
+        <v>0.009785245999999999</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.00366001</v>
+        <v>-0.003100619</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>934.964663045</v>
+        <v>934.973496008</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.001171286</v>
+        <v>0.005821684</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.004067527</v>
+        <v>0.004293154</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8344,20 +8344,20 @@
         <v>-0.016820258</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.03313443</v>
+        <v>-0.033126522</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.014622045</v>
+        <v>-0.014611229</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.040588938</v>
+        <v>0.040610508</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.017983579</v>
+        <v>-0.017952796</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.032273162</v>
+        <v>-0.032222753</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8472,20 +8472,20 @@
         <v>0.013002672</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.024859155</v>
+        <v>0.024853222</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.010349441</v>
+        <v>0.010341485</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.028018681</v>
+        <v>-0.028034051</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.01329038</v>
+        <v>0.013268551</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.023114667</v>
+        <v>0.023081385</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9148,11 +9148,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>82000</v>
+        <v>78100</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 78,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 82,900원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1826198982641148</v>
+        <v>0.1826160454187842</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07578076200067632</v>
+        <v>0.07578071715021344</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02310819356317076</v>
+        <v>0.02311770437506521</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.04268507342716227</v>
+        <v>0.04269136362322838</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33839,7 +33839,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41112,7 +41112,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>168.48</v>
+        <v>160.47</v>
       </c>
     </row>
     <row r="32">
@@ -41122,7 +41122,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -681,37 +681,37 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 161069억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 160141억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169896억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167314억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 178685억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 175973억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164865억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164233억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164256억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169448억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 162764억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 177774억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 161069억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 160141억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169896억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167314억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 178685억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 175973억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164865억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164233억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164256억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169448억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 162764억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 177774억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2034,31 +2034,31 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 21911억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 21908억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22455억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22441억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22687억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22667억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22051억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22029억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22344억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 22337억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2094,31 +2094,31 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 21911억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 21908억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22455억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22441억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22687억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22667억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22051억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22029억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 22344억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 22337억 × 2.31%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 32608억 × 4.27%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4174,7 +4174,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6451,23 +6451,23 @@
         <v>0.077089358</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.26688849</v>
+        <v>0.259587778</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.329026526</v>
+        <v>0.30882849</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.390508</v>
+        <v>0.369401167</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.099141566</v>
+        <v>0.094932055</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.019789578</v>
+        <v>0.058117251</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.041983055</v>
+        <v>0.062517503</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6765,26 +6765,26 @@
         <v>0.044952119</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.044952253</v>
+        <v>0.044952074</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.044952331</v>
+        <v>0.044952513</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.044952244</v>
+        <v>0.044952164</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.044952534</v>
+        <v>0.044952362</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.044952106</v>
+        <v>0.044952308</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.044952487</v>
+        <v>0.04495234</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7944,36 +7944,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.01110209</v>
+        <v>0.011852057</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.003120246</v>
+        <v>0.00334389</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.007004925</v>
+        <v>0.007058732</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>934.962964736</v>
+        <v>934.962650654</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.005121293</v>
+        <v>0.005707541</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.009785245999999999</v>
+        <v>0.003110956</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>-0.003100619</v>
+        <v>0.006903242</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>934.973496008</v>
+        <v>934.962771862</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.005821684</v>
+        <v>0.01091221</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.004293154</v>
+        <v>0.003448653</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.01120209</v>
+        <v>0.011952057</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.003120246</v>
+        <v>0.00334389</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.007004925</v>
+        <v>0.007058732</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>934.962964736</v>
+        <v>934.962650654</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.005121293</v>
+        <v>0.005707541</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.009785245999999999</v>
+        <v>0.003110956</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.003100619</v>
+        <v>0.006903242</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>934.973496008</v>
+        <v>934.962771862</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.005821684</v>
+        <v>0.01091221</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.004293154</v>
+        <v>0.003448653</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8341,23 +8341,23 @@
         <v>0.042501997</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>-0.016820258</v>
+        <v>-0.016656978</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.033126522</v>
+        <v>-0.032440415</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.014611229</v>
+        <v>-0.014192984</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.040610508</v>
+        <v>0.040682741</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.017952796</v>
+        <v>-0.01885715</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.032222753</v>
+        <v>-0.036263952</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8469,23 +8469,23 @@
         <v>-0.03055256</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.013002672</v>
+        <v>0.012876455</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.024853222</v>
+        <v>0.024345545</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.010341485</v>
+        <v>0.010060928</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.028034051</v>
+        <v>-0.028146142</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.013268551</v>
+        <v>0.013970183</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.023081385</v>
+        <v>0.025996102</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1826160454187842</v>
+        <v>0.1826172257167381</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07578071715021344</v>
+        <v>0.07578074320686151</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02311770437506521</v>
+        <v>0.02311054619887206</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.04269136362322838</v>
+        <v>0.04268645806825206</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 167314억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 167299억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 175973억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 175957억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 164233억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 164217억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 169448억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 169430억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−4) 177774억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
+고객지수 4분기 이동합(t−4) 177772억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 167314억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 167299억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 175973억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 175957억 × 비례계수 0.3421 × 계절비중 Q1 0.187(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 164233억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 164217억 × 비례계수 0.3421 × 계절비중 Q2 0.235(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 169448억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 169430억 × 비례계수 0.3421 × 계절비중 Q3 0.234(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−4) 177774억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−4) 177772억 × 비례계수 0.3421 × 계절비중 Q4 0.344(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.98, n=8, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -5045,35 +5045,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5164,35 +5164,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5283,35 +5283,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5402,35 +5402,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5521,35 +5521,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5640,35 +5640,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5759,35 +5759,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5878,35 +5878,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6013,7 +6013,7 @@
         <v>75200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>78100</v>
+        <v>76700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6195,7 +6195,7 @@
         <v>50700</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>72800</v>
+        <v>72500</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6286,7 +6286,7 @@
         <v>70688.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>80150</v>
+        <v>79380</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6454,20 +6454,20 @@
         <v>0.259587778</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.30882849</v>
+        <v>0.308710295</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.369401167</v>
+        <v>0.369278453</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.094932055</v>
+        <v>0.094822394</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.058117251</v>
+        <v>0.058010306</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.062517503</v>
+        <v>0.062597734</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6768,23 +6768,23 @@
         <v>0.044952074</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.044952513</v>
+        <v>0.044952514</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.044952164</v>
+        <v>0.044952644</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.044952362</v>
+        <v>0.044952312</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.044952308</v>
+        <v>0.044952425</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.04495234</v>
+        <v>0.04495205</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7944,36 +7944,36 @@
         <v/>
       </c>
       <c r="AC31" s="30" t="n">
-        <v>0.011852057</v>
+        <v>0.011417319</v>
       </c>
       <c r="AD31" s="30" t="n">
-        <v>0.00334389</v>
+        <v>0.002244122</v>
       </c>
       <c r="AE31" s="31" t="n"/>
       <c r="AF31" s="30" t="n">
-        <v>0.007058732</v>
+        <v>0.00608749</v>
       </c>
       <c r="AG31" s="30" t="n">
-        <v>934.962650654</v>
+        <v>934.961198706</v>
       </c>
       <c r="AH31" s="30" t="n">
-        <v>0.005707541</v>
+        <v>0.005073674</v>
       </c>
       <c r="AI31" s="30" t="n">
-        <v>0.003110956</v>
+        <v>0.006122599</v>
       </c>
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="30" t="n">
-        <v>0.006903242</v>
+        <v>0.002377207</v>
       </c>
       <c r="AL31" s="30" t="n">
-        <v>934.962771862</v>
+        <v>934.971245443</v>
       </c>
       <c r="AM31" s="30" t="n">
-        <v>0.01091221</v>
+        <v>-5.6566e-05</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>0.003448653</v>
+        <v>-0.006117513</v>
       </c>
       <c r="AO31" s="31" t="n"/>
     </row>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="AC32" s="30" t="n">
-        <v>0.011952057</v>
+        <v>0.011517319</v>
       </c>
       <c r="AD32" s="30" t="n">
-        <v>0.00334389</v>
+        <v>0.002244122</v>
       </c>
       <c r="AE32" s="31" t="n"/>
       <c r="AF32" s="30" t="n">
-        <v>0.007058732</v>
+        <v>0.00608749</v>
       </c>
       <c r="AG32" s="30" t="n">
-        <v>934.962650654</v>
+        <v>934.961198706</v>
       </c>
       <c r="AH32" s="30" t="n">
-        <v>0.005707541</v>
+        <v>0.005073674</v>
       </c>
       <c r="AI32" s="30" t="n">
-        <v>0.003110956</v>
+        <v>0.006122599</v>
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>0.006903242</v>
+        <v>0.002377207</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>934.962771862</v>
+        <v>934.971245443</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>0.01091221</v>
+        <v>-5.6566e-05</v>
       </c>
       <c r="AN32" s="30" t="n">
-        <v>0.003448653</v>
+        <v>-0.006117513</v>
       </c>
       <c r="AO32" s="31" t="n"/>
     </row>
@@ -8344,20 +8344,20 @@
         <v>-0.016656978</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>-0.032440415</v>
+        <v>-0.032436766</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>-0.014192984</v>
+        <v>-0.014190416</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.040682741</v>
+        <v>0.04068567</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>-0.01885715</v>
+        <v>-0.018853913</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>-0.036263952</v>
+        <v>-0.03626225</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8472,20 +8472,20 @@
         <v>0.012876455</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.024345545</v>
+        <v>0.024342806</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.010060928</v>
+        <v>0.010059172</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.028146142</v>
+        <v>-0.028148472</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.013970183</v>
+        <v>0.013968008</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.025996102</v>
+        <v>0.02599544</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9148,11 +9148,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>78100</v>
+        <v>76700</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 82,900원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 81,700원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9188,7 +9188,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.1826172257167381</v>
+        <v>0.182619177453147</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.07578074320686151</v>
+        <v>0.07578073422990672</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02311054619887206</v>
+        <v>0.02310424127913647</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.04268645806825206</v>
+        <v>0.04268227121955757</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41112,7 +41112,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>160.47</v>
+        <v>157.59</v>
       </c>
     </row>
     <row r="32">
@@ -41122,7 +41122,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5255,35 +5255,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5374,35 +5374,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5493,35 +5493,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5612,35 +5612,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5731,35 +5731,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5850,35 +5850,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5969,35 +5969,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6088,35 +6088,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8329,13 +8329,13 @@
       </c>
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="30" t="n">
-        <v>-0.004665419</v>
+        <v>-0.00466542</v>
       </c>
       <c r="AL32" s="30" t="n">
-        <v>934.974609676</v>
+        <v>934.974609677</v>
       </c>
       <c r="AM32" s="30" t="n">
-        <v>-0.00503827</v>
+        <v>-0.005038271</v>
       </c>
       <c r="AN32" s="30" t="n">
         <v>0.003419515</v>
@@ -8457,13 +8457,13 @@
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>-0.004665419</v>
+        <v>-0.00466542</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>934.974609676</v>
+        <v>934.974609677</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>-0.00503827</v>
+        <v>-0.005038271</v>
       </c>
       <c r="AN33" s="30" t="n">
         <v>0.003419515</v>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 81,700원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 77,600원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02312773562519193</v>
+        <v>0.02312773562518853</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04269831551303502</v>
+        <v>0.04269831551303982</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -4384,7 +4384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5255,35 +5255,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5374,35 +5374,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5493,35 +5493,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5612,35 +5612,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5731,35 +5731,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5850,35 +5850,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5969,35 +5969,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6088,35 +6088,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -4384,7 +4384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -4384,7 +4384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6223,7 @@
         <v>75200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>76700</v>
+        <v>75100</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6496,7 +6496,7 @@
         <v>70688.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>79380</v>
+        <v>78666.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>76700</v>
+        <v>75100</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39611,7 +39611,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41795,7 +41795,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>98.52</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="32">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -4384,7 +4384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5255,35 +5255,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5374,35 +5374,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5493,35 +5493,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5612,35 +5612,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5731,35 +5731,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5850,35 +5850,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5969,35 +5969,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6088,35 +6088,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6223,7 +6223,7 @@
         <v>75200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>75100</v>
+        <v>77500</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6405,7 +6405,7 @@
         <v>50700</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>72500</v>
+        <v>71100</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6496,7 +6496,7 @@
         <v>70688.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>78666.7</v>
+        <v>78414.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9513,11 +9513,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>75100</v>
+        <v>77500</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 77,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 76,600원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39611,7 +39611,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41795,7 +41795,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>96.47</v>
+        <v>99.55</v>
       </c>
     </row>
     <row r="32">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -4384,7 +4384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5255,35 +5255,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5374,35 +5374,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5493,35 +5493,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5612,35 +5612,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5731,35 +5731,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5850,35 +5850,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5969,35 +5969,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6088,35 +6088,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6223,7 +6223,7 @@
         <v>75200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>77500</v>
+        <v>80800</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6496,7 +6496,7 @@
         <v>70688.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>78414.3</v>
+        <v>78712.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9513,11 +9513,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>77500</v>
+        <v>80800</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 76,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 75,100원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39611,7 +39611,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41795,7 +41795,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>99.55</v>
+        <v>103.79</v>
       </c>
     </row>
     <row r="32">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -4384,7 +4384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5255,35 +5255,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5374,35 +5374,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5493,35 +5493,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5612,35 +5612,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5731,35 +5731,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5850,35 +5850,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5969,35 +5969,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6088,35 +6088,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6223,7 +6223,7 @@
         <v>75200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>80800</v>
+        <v>82000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6496,7 +6496,7 @@
         <v>70688.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>78712.5</v>
+        <v>78718.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>80800</v>
+        <v>82000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39611,7 +39611,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41795,7 +41795,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>103.79</v>
+        <v>105.33</v>
       </c>
     </row>
     <row r="32">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.36</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/272210_model.xlsx
+++ b/argus/kship/models/272210_model.xlsx
@@ -4384,7 +4384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5255,35 +5255,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5374,35 +5374,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5493,35 +5493,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5612,35 +5612,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5731,35 +5731,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5850,35 +5850,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5969,35 +5969,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6088,35 +6088,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6223,7 +6223,7 @@
         <v>75200</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>82000</v>
+        <v>63000</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6405,7 +6405,7 @@
         <v>50700</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>71100</v>
+        <v>60100</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6496,7 +6496,7 @@
         <v>70688.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>78718.2</v>
+        <v>75718.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9513,11 +9513,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>82000</v>
+        <v>63000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 75,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 73,900원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34350,7 +34350,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39611,7 +39611,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41795,7 +41795,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>105.33</v>
+        <v>80.92</v>
       </c>
     </row>
     <row r="32">
@@ -41805,7 +41805,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.41</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="33">
